--- a/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_見込量保険料算定シート_20260909.xlsx
+++ b/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_見込量保険料算定シート_20260909.xlsx
@@ -120,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -203,10 +203,10 @@
     <xf numFmtId="3" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -220,9 +220,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -1139,7 +1136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1230,11 +1227,11 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>総費用額（3年計）</t>
+          <t xml:space="preserve">　うち介護予防・日常生活支援総合事業費（3年計）</t>
         </is>
       </c>
       <c r="C4" s="22">
-        <f>C2+C3</f>
+        <f>SUM('07_地域支援事業'!D2:D6)+SUM('07_地域支援事業'!E2:E6)+SUM('07_地域支援事業'!F2:F6)</f>
         <v/>
       </c>
       <c r="D4" s="8" t="inlineStr">
@@ -1244,7 +1241,7 @@
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>①＋②</t>
+          <t>**調整交付金は総合事業費にのみかかる。包括的支援事業・任意事業は対象外**</t>
         </is>
       </c>
     </row>
@@ -1254,18 +1251,21 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>第1号被保険者負担割合</t>
-        </is>
-      </c>
-      <c r="C5" s="28" t="n"/>
+          <t>総費用額（3年計）</t>
+        </is>
+      </c>
+      <c r="C5" s="22">
+        <f>C2+C3</f>
+        <v/>
+      </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>％</t>
+          <t>千円</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>国の基本指針による。第9期は23％。**第10期の割合は国の決定後に確定**</t>
+          <t>①＋②</t>
         </is>
       </c>
     </row>
@@ -1275,21 +1275,20 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>第1号被保険者負担分相当額</t>
-        </is>
-      </c>
-      <c r="C6" s="22">
-        <f>C4*C5/100</f>
-        <v/>
+          <t>第1号被保険者負担割合</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="n">
+        <v>23</v>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>千円</t>
+          <t>％</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>③×④</t>
+          <t>**3年の計画期間ごとに政令で定める。第9期（令和6〜8年度）は23％。**第1期17％から3年ごとに1ptずつ上がってきており、第10期は24％となる可能性がある。第10期に適用される政令の公布状況を確認すること</t>
         </is>
       </c>
     </row>
@@ -1299,11 +1298,11 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>調整交付金相当額</t>
+          <t>第1号被保険者負担分相当額</t>
         </is>
       </c>
       <c r="C7" s="22">
-        <f>C4*C8/100</f>
+        <f>C5*C6/100</f>
         <v/>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -1313,7 +1312,7 @@
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>③×⑦</t>
+          <t>④×⑤</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1325,9 @@
           <t>調整交付金相当割合</t>
         </is>
       </c>
-      <c r="C8" s="28" t="n"/>
+      <c r="C8" s="28" t="n">
+        <v>5</v>
+      </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
           <t>％</t>
@@ -1344,10 +1345,13 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>調整交付金見込額</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="n"/>
+          <t>調整交付金相当額</t>
+        </is>
+      </c>
+      <c r="C9" s="22">
+        <f>(C2+C4)*C8/100</f>
+        <v/>
+      </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
           <t>千円</t>
@@ -1355,7 +1359,7 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>**後期高齢者加入割合・所得段階別加入割合により算定。見える化システムで確認**</t>
+          <t>（①＋③）×⑦</t>
         </is>
       </c>
     </row>
@@ -1365,18 +1369,20 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>財政安定化基金拠出金見込額</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="n"/>
+          <t>調整交付金見込交付割合</t>
+        </is>
+      </c>
+      <c r="C10" s="29" t="n">
+        <v>5.963</v>
+      </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>千円</t>
+          <t>％</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>県の設定による。第9期は0円</t>
+          <t>**第9期計画の公表値から逆算した小野町の実績値。**（①＋③）×23％＋（①＋③）×5％－保険料収納必要額832,562千円 より5.963％。後期高齢者加入割合が高く低所得層が厚い保険者ほど5％を上回る。**第10期の値は見える化システムの係数シート（全国値）で確認する**</t>
         </is>
       </c>
     </row>
@@ -1386,10 +1392,13 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>財政安定化基金償還金</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="n"/>
+          <t>調整交付金見込額</t>
+        </is>
+      </c>
+      <c r="C11" s="22">
+        <f>(C2+C4)*C10/100</f>
+        <v/>
+      </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
           <t>千円</t>
@@ -1397,7 +1406,7 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>借入がある場合。第9期は0円</t>
+          <t>（①＋③）×⑨</t>
         </is>
       </c>
     </row>
@@ -1407,10 +1416,12 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>準備基金取崩額</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="n"/>
+          <t>財政安定化基金拠出金見込額</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
           <t>千円</t>
@@ -1418,7 +1429,7 @@
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>**政策判断。第9期は35,000千円を見込んだが、介護給付費準備基金の保有額は令和5・6年度末とも12,000千円しかない（年報 様式4）。**取崩の原資が足りるかを確認したうえで設定する。ケースC5・C6で変える</t>
+          <t>県の設定による。第9期は0円</t>
         </is>
       </c>
     </row>
@@ -1428,10 +1439,12 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>市町村特別給付費等</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="n"/>
+          <t>財政安定化基金償還金</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
           <t>千円</t>
@@ -1439,7 +1452,7 @@
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>町単独事業を保険料で賄う場合</t>
+          <t>借入がある場合。第9期は0円</t>
         </is>
       </c>
     </row>
@@ -1449,13 +1462,10 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>保険料収納必要額</t>
-        </is>
-      </c>
-      <c r="C14" s="22">
-        <f>C6+C7-C9+C10+C11-C12+C13</f>
-        <v/>
-      </c>
+          <t>準備基金取崩額</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="n"/>
       <c r="D14" s="8" t="inlineStr">
         <is>
           <t>千円</t>
@@ -1463,7 +1473,7 @@
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>⑤＋⑥－⑧＋⑨＋⑩－⑪＋⑫</t>
+          <t>**政策判断。第9期は35,000千円を見込んだが、介護給付費準備基金の保有額は令和5・6年度末とも12,000千円しかない（年報 様式4）。**取崩の原資が足りるかを確認したうえで設定する。ケースC5・C6で変える</t>
         </is>
       </c>
     </row>
@@ -1473,20 +1483,20 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>予定保険料収納率</t>
-        </is>
-      </c>
-      <c r="C15" s="29" t="n">
-        <v>99.34999999999999</v>
+          <t>市町村特別給付費等</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>％</t>
+          <t>千円</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>**令和7年度実績＝収納264,162,900円÷調定265,881,800円＝99.35％（年報 様式3）。**直近3年の実績を踏まえて設定する</t>
+          <t>町単独事業を保険料で賄う場合</t>
         </is>
       </c>
     </row>
@@ -1496,11 +1506,11 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>保険料賦課総額</t>
+          <t>保険料収納必要額</t>
         </is>
       </c>
       <c r="C16" s="22">
-        <f>IF(C15=0,"",C14/C15*100)</f>
+        <f>C7+C9-C11+C12+C13-C14+C15</f>
         <v/>
       </c>
       <c r="D16" s="8" t="inlineStr">
@@ -1510,7 +1520,7 @@
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>⑬÷⑭</t>
+          <t>⑥＋⑧－⑩＋⑪＋⑫－⑬＋⑭</t>
         </is>
       </c>
     </row>
@@ -1520,21 +1530,20 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>所得段階別加入割合補正後被保険者数（3年計）</t>
-        </is>
-      </c>
-      <c r="C17" s="22">
-        <f>E37</f>
-        <v/>
+          <t>予定保険料収納率</t>
+        </is>
+      </c>
+      <c r="C17" s="28" t="n">
+        <v>99.34999999999999</v>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>人</t>
+          <t>％</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>下表の合計。**所得段階別第1号被保険者数が必要**</t>
+          <t>**令和7年度実績＝収納264,162,900円÷調定265,881,800円＝99.35％（年報 様式3）。**直近3年の実績を踏まえて設定する</t>
         </is>
       </c>
     </row>
@@ -1542,18 +1551,18 @@
       <c r="A18" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="23" t="inlineStr">
-        <is>
-          <t>保険料基準額（年額）</t>
-        </is>
-      </c>
-      <c r="C18" s="30">
-        <f>IF(C17=0,"",C16*1000/C17)</f>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>保険料賦課総額</t>
+        </is>
+      </c>
+      <c r="C18" s="22">
+        <f>IF(C17=0,"",C16/C17*100)</f>
         <v/>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>円</t>
+          <t>千円</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
@@ -1566,23 +1575,23 @@
       <c r="A19" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="23" t="inlineStr">
-        <is>
-          <t>保険料基準額（月額）</t>
-        </is>
-      </c>
-      <c r="C19" s="30">
-        <f>IF(C18="","",C18/12)</f>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>所得段階別加入割合補正後被保険者数（3年計）</t>
+        </is>
+      </c>
+      <c r="C19" s="22">
+        <f>E39</f>
         <v/>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>円</t>
+          <t>人</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>⑰÷12</t>
+          <t>下表の合計</t>
         </is>
       </c>
     </row>
@@ -1590,13 +1599,14 @@
       <c r="A20" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>第9期の保険料基準額（月額）</t>
-        </is>
-      </c>
-      <c r="C20" s="31" t="n">
-        <v>6600</v>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>保険料基準額（年額）</t>
+        </is>
+      </c>
+      <c r="C20" s="30">
+        <f>IF(C19=0,"",C18*1000/C19)</f>
+        <v/>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
@@ -1605,7 +1615,7 @@
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>第9期計画本文</t>
+          <t>⑰÷⑱</t>
         </is>
       </c>
     </row>
@@ -1615,122 +1625,125 @@
       </c>
       <c r="B21" s="23" t="inlineStr">
         <is>
+          <t>保険料基準額（月額）</t>
+        </is>
+      </c>
+      <c r="C21" s="30">
+        <f>IF(C20="","",C20/12)</f>
+        <v/>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>円</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>⑲÷12</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>第9期の保険料基準額（月額）</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n">
+        <v>6600</v>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>円</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>第9期計画本文</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
           <t>第9期との差</t>
         </is>
       </c>
-      <c r="C21" s="30">
-        <f>IF(C19="","",C19-C20)</f>
-        <v/>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="C23" s="30">
+        <f>IF(C21="","",C21-C22)</f>
+        <v/>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>円</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>⑱－⑲</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="19" t="inlineStr">
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>⑳－㉑</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>【所得段階別 加入割合補正後被保険者数】</t>
         </is>
       </c>
-      <c r="B22" s="18" t="n"/>
-      <c r="C22" s="17" t="n"/>
-      <c r="D22" s="17" t="n"/>
-      <c r="E22" s="17" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="32" t="inlineStr">
+      <c r="B24" s="18" t="n"/>
+      <c r="C24" s="17" t="n"/>
+      <c r="D24" s="17" t="n"/>
+      <c r="E24" s="17" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="32" t="inlineStr">
         <is>
           <t>段階</t>
         </is>
       </c>
-      <c r="B23" s="33" t="inlineStr">
+      <c r="B25" s="33" t="inlineStr">
         <is>
           <t>対象</t>
         </is>
       </c>
-      <c r="C23" s="32" t="inlineStr">
+      <c r="C25" s="32" t="inlineStr">
         <is>
           <t>保険料率</t>
         </is>
       </c>
-      <c r="D23" s="32" t="inlineStr">
+      <c r="D25" s="32" t="inlineStr">
         <is>
           <t>被保険者数（3年計）</t>
         </is>
       </c>
-      <c r="E23" s="32" t="inlineStr">
+      <c r="E25" s="32" t="inlineStr">
         <is>
           <t>補正後人数</t>
         </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>第1段階</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>生活保護受給者、老齢福祉年金受給者、住民税非課税世帯かつ年金収入等80万円以下</t>
-        </is>
-      </c>
-      <c r="C24" s="34" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="D24" s="11" t="n">
-        <v>1575</v>
-      </c>
-      <c r="E24" s="21">
-        <f>IF(D24="","",C24*D24)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>第2段階</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>住民税非課税世帯かつ年金収入等80万円超120万円以下</t>
-        </is>
-      </c>
-      <c r="C25" s="34" t="n">
-        <v>0.486</v>
-      </c>
-      <c r="D25" s="11" t="n">
-        <v>891</v>
-      </c>
-      <c r="E25" s="21">
-        <f>IF(D25="","",C25*D25)</f>
-        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>第3段階</t>
+          <t>第1段階</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>住民税非課税世帯かつ年金収入等120万円超</t>
-        </is>
-      </c>
-      <c r="C26" s="34" t="n">
-        <v>0.6850000000000001</v>
+          <t>生活保護受給者、老齢福祉年金受給者、住民税非課税世帯かつ年金収入等80万円以下</t>
+        </is>
+      </c>
+      <c r="C26" s="29" t="n">
+        <v>0.285</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>816</v>
+        <v>1568</v>
       </c>
       <c r="E26" s="21">
         <f>IF(D26="","",C26*D26)</f>
@@ -1740,19 +1753,19 @@
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>第4段階</t>
+          <t>第2段階</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>本人非課税かつ世帯課税、年金収入等80万円以下</t>
-        </is>
-      </c>
-      <c r="C27" s="34" t="n">
-        <v>0.9</v>
+          <t>住民税非課税世帯かつ年金収入等80万円超120万円以下</t>
+        </is>
+      </c>
+      <c r="C27" s="29" t="n">
+        <v>0.486</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>1302</v>
+        <v>887</v>
       </c>
       <c r="E27" s="21">
         <f>IF(D27="","",C27*D27)</f>
@@ -1762,19 +1775,19 @@
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>第5段階</t>
+          <t>第3段階</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>本人非課税かつ世帯課税、年金収入等80万円超</t>
-        </is>
-      </c>
-      <c r="C28" s="34" t="n">
-        <v>1</v>
+          <t>住民税非課税世帯かつ年金収入等120万円超</t>
+        </is>
+      </c>
+      <c r="C28" s="29" t="n">
+        <v>0.6850000000000001</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>1830</v>
+        <v>812</v>
       </c>
       <c r="E28" s="21">
         <f>IF(D28="","",C28*D28)</f>
@@ -1784,19 +1797,19 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>第6段階</t>
+          <t>第4段階</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>本人課税、合計所得金額120万円未満</t>
-        </is>
-      </c>
-      <c r="C29" s="34" t="n">
-        <v>1.2</v>
+          <t>本人非課税かつ世帯課税、年金収入等80万円以下</t>
+        </is>
+      </c>
+      <c r="C29" s="29" t="n">
+        <v>0.9</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1473</v>
+        <v>1296</v>
       </c>
       <c r="E29" s="21">
         <f>IF(D29="","",C29*D29)</f>
@@ -1806,19 +1819,19 @@
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>第7段階</t>
+          <t>第5段階</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>本人課税、合計所得金額120万円以上210万円未満</t>
-        </is>
-      </c>
-      <c r="C30" s="34" t="n">
-        <v>1.3</v>
+          <t>本人非課税かつ世帯課税、年金収入等80万円超</t>
+        </is>
+      </c>
+      <c r="C30" s="29" t="n">
+        <v>1</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>1254</v>
+        <v>1822</v>
       </c>
       <c r="E30" s="21">
         <f>IF(D30="","",C30*D30)</f>
@@ -1828,19 +1841,19 @@
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>第8段階</t>
+          <t>第6段階</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>本人課税、合計所得金額210万円以上320万円未満</t>
-        </is>
-      </c>
-      <c r="C31" s="34" t="n">
-        <v>1.5</v>
+          <t>本人課税、合計所得金額120万円未満</t>
+        </is>
+      </c>
+      <c r="C31" s="29" t="n">
+        <v>1.2</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>693</v>
+        <v>1467</v>
       </c>
       <c r="E31" s="21">
         <f>IF(D31="","",C31*D31)</f>
@@ -1850,19 +1863,19 @@
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>第9段階</t>
+          <t>第7段階</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>本人課税、合計所得金額320万円以上420万円未満</t>
-        </is>
-      </c>
-      <c r="C32" s="34" t="n">
-        <v>1.7</v>
+          <t>本人課税、合計所得金額120万円以上210万円未満</t>
+        </is>
+      </c>
+      <c r="C32" s="29" t="n">
+        <v>1.3</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>231</v>
+        <v>1249</v>
       </c>
       <c r="E32" s="21">
         <f>IF(D32="","",C32*D32)</f>
@@ -1872,19 +1885,19 @@
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>第10段階</t>
+          <t>第8段階</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>本人課税、合計所得金額420万円以上520万円未満</t>
-        </is>
-      </c>
-      <c r="C33" s="34" t="n">
-        <v>1.9</v>
+          <t>本人課税、合計所得金額210万円以上320万円未満</t>
+        </is>
+      </c>
+      <c r="C33" s="29" t="n">
+        <v>1.5</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>108</v>
+        <v>690</v>
       </c>
       <c r="E33" s="21">
         <f>IF(D33="","",C33*D33)</f>
@@ -1894,19 +1907,19 @@
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>第11段階</t>
+          <t>第9段階</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>本人課税、合計所得金額520万円以上620万円未満</t>
-        </is>
-      </c>
-      <c r="C34" s="34" t="n">
-        <v>2.1</v>
+          <t>本人課税、合計所得金額320万円以上420万円未満</t>
+        </is>
+      </c>
+      <c r="C34" s="29" t="n">
+        <v>1.7</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>42</v>
+        <v>230</v>
       </c>
       <c r="E34" s="21">
         <f>IF(D34="","",C34*D34)</f>
@@ -1916,19 +1929,19 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>第12段階</t>
+          <t>第10段階</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>本人課税、合計所得金額620万円以上720万円未満</t>
-        </is>
-      </c>
-      <c r="C35" s="34" t="n">
-        <v>2.3</v>
+          <t>本人課税、合計所得金額420万円以上520万円未満</t>
+        </is>
+      </c>
+      <c r="C35" s="29" t="n">
+        <v>1.9</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="E35" s="21">
         <f>IF(D35="","",C35*D35)</f>
@@ -1938,19 +1951,19 @@
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>第13段階</t>
+          <t>第11段階</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>本人課税、合計所得金額720万円以上</t>
-        </is>
-      </c>
-      <c r="C36" s="34" t="n">
-        <v>2.4</v>
+          <t>本人課税、合計所得金額520万円以上620万円未満</t>
+        </is>
+      </c>
+      <c r="C36" s="29" t="n">
+        <v>2.1</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="E36" s="21">
         <f>IF(D36="","",C36*D36)</f>
@@ -1960,38 +1973,89 @@
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
+          <t>第12段階</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>本人課税、合計所得金額620万円以上720万円未満</t>
+        </is>
+      </c>
+      <c r="C37" s="29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D37" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="E37" s="21">
+        <f>IF(D37="","",C37*D37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>第13段階</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>本人課税、合計所得金額720万円以上</t>
+        </is>
+      </c>
+      <c r="C38" s="29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D38" s="11" t="n">
+        <v>93</v>
+      </c>
+      <c r="E38" s="21">
+        <f>IF(D38="","",C38*D38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B37" s="9" t="inlineStr"/>
-      <c r="C37" s="8" t="inlineStr"/>
-      <c r="D37" s="24">
-        <f>SUM(D24:D36)</f>
-        <v/>
-      </c>
-      <c r="E37" s="24">
-        <f>SUM(E24:E36)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>※ **保険料率は小野町が第9期で定めた割合（年報 様式1 所得段階別）。**第1〜3段階は国の標準（0.455／0.685／0.69）より低い0.285／0.486／0.685で、公費による低所得者軽減を反映した率です。第10期の段階設定は国の基本指針を受けて確定します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>※ **被保険者数は令和7年度末の実績（年報 様式1 所得段階別）を3倍して3年計としています。**計画期間の被保険者数の推移（02_人口・被保険者）に応じて置き換えてください。</t>
-        </is>
+      <c r="B39" s="9" t="inlineStr"/>
+      <c r="C39" s="8" t="inlineStr"/>
+      <c r="D39" s="24">
+        <f>SUM(D26:D38)</f>
+        <v/>
+      </c>
+      <c r="E39" s="24">
+        <f>SUM(E26:E38)</f>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>※ 補正後人数＝保険料率×被保険者数。</t>
+          <t>※ **保険料率は小野町が第9期で定めた割合（年報 様式1 所得段階別）。**第1〜3段階は国の標準（0.455／0.685／0.69）より低い0.285／0.486／0.685で、公費による低所得者軽減を反映した率です。第10期の段階設定は国の基本指針を受けて確定します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>※ **被保険者数は令和7年度末の段階別構成比（年報 様式1 所得段階別・計3,443人）を、第10期3年分の第1号被保険者数10,284人に当てたものです。**実績をそのまま3倍すると計画期間の人口減が落ちます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>※ 補正後人数＝保険料率×被保険者数。この合計÷被保険者数の合計が「所得段階別加入割合補正係数」で、調整交付金の算定にも用います。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>※ **第9期の算定における補正係数は0.968でしたが、令和7年度実績では0.952です。**低所得段階の割合が上がっており、同じ賦課総額でも基準額が上がる方向に働きます。第9期の算定に用いた所得段階別人数の年度を町に確認してください。</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2137,7 @@
           <t>C1 標準（低位）</t>
         </is>
       </c>
-      <c r="B2" s="35" t="n"/>
+      <c r="B2" s="34" t="n"/>
       <c r="C2" s="10" t="n"/>
       <c r="D2" s="10" t="n"/>
       <c r="E2" s="10" t="n"/>
@@ -2088,7 +2152,7 @@
           <t>C2 標準（高位）</t>
         </is>
       </c>
-      <c r="B3" s="35" t="n"/>
+      <c r="B3" s="34" t="n"/>
       <c r="C3" s="10" t="n"/>
       <c r="D3" s="10" t="n"/>
       <c r="E3" s="10" t="n"/>
@@ -2103,7 +2167,7 @@
           <t>C3 施設整備あり</t>
         </is>
       </c>
-      <c r="B4" s="35" t="n"/>
+      <c r="B4" s="34" t="n"/>
       <c r="C4" s="10" t="n"/>
       <c r="D4" s="10" t="n"/>
       <c r="E4" s="10" t="n"/>
@@ -2118,7 +2182,7 @@
           <t>C4 制度改正の影響</t>
         </is>
       </c>
-      <c r="B5" s="35" t="n"/>
+      <c r="B5" s="34" t="n"/>
       <c r="C5" s="10" t="n"/>
       <c r="D5" s="10" t="n"/>
       <c r="E5" s="10" t="n"/>
@@ -2133,7 +2197,7 @@
           <t>C5 基金活用</t>
         </is>
       </c>
-      <c r="B6" s="35" t="n"/>
+      <c r="B6" s="34" t="n"/>
       <c r="C6" s="10" t="n"/>
       <c r="D6" s="10" t="n"/>
       <c r="E6" s="10" t="n"/>
@@ -2148,7 +2212,7 @@
           <t>C6 保険料据置（逆算）</t>
         </is>
       </c>
-      <c r="B7" s="35" t="n"/>
+      <c r="B7" s="34" t="n"/>
       <c r="C7" s="10" t="n"/>
       <c r="D7" s="10" t="n"/>
       <c r="E7" s="10" t="n"/>
@@ -2237,7 +2301,7 @@
           <t>要支援・要介護認定者数（令和8年3月末）</t>
         </is>
       </c>
-      <c r="C2" s="36" t="n">
+      <c r="C2" s="35" t="n">
         <v>792</v>
       </c>
       <c r="D2" s="8" t="inlineStr">
@@ -2912,7 +2976,7 @@
           <t>収納率（現年度分）</t>
         </is>
       </c>
-      <c r="C29" s="37" t="n">
+      <c r="C29" s="36" t="n">
         <v>0.9935</v>
       </c>
       <c r="D29" s="8" t="inlineStr">
